--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mengzi/Desktop/TUD/ME44305_SAS/ME44305-SAS-1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mengzi/Desktop/TUD/ME44305_SAS/ME44305-SAS-1/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766BFF06-857F-F841-BDB3-9A619FB237DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB90E0AD-2DFA-234C-AF19-80320290A6B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="900" windowWidth="29080" windowHeight="16940" xr2:uid="{9E9FA2F7-E068-6B42-9C97-82BE8A40D8EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v2.0" hidden="1">Sheet1!$G$3:$G$6</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -678,5 +681,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>